--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5522AE25-D0EB-4868-9594-E4EBFA02293C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8EE538-8280-47CF-BAFA-C964E4E469B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -137,6 +137,42 @@
   </si>
   <si>
     <t>1001,1,500&amp;1001,1,500&amp;1002,2,500&amp;1003,1,500&amp;1004,1,500&amp;5003,1,10000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光星阵</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>时光星阵，消耗星阵币 * 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,500&amp;1002,1,500&amp;1003,1,500&amp;1004,1,500</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>106,1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>additionRewards</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,5&amp;1002,10&amp;1003,20&amp;1004,50&amp;1001,5&amp;1002,10&amp;1003,20&amp;1004,50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>c,s</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>额外奖励</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -472,17 +508,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" customWidth="1"/>
-    <col min="5" max="5" width="82.88671875" customWidth="1"/>
-    <col min="6" max="6" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="51.875" customWidth="1"/>
+    <col min="5" max="5" width="82.875" customWidth="1"/>
+    <col min="6" max="6" width="13.75" customWidth="1"/>
+    <col min="7" max="7" width="44.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -501,8 +538,11 @@
       <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -521,8 +561,11 @@
       <c r="F2" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -541,8 +584,11 @@
       <c r="F3" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -561,8 +607,11 @@
       <c r="F4" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -579,7 +628,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -596,7 +645,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -611,6 +660,26 @@
       </c>
       <c r="F7" s="1" t="s">
         <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8EE538-8280-47CF-BAFA-C964E4E469B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED63E99-DC61-463C-9633-AA468F84B8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED63E99-DC61-463C-9633-AA468F84B8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B92AE5B9-9CC1-4CCB-9D43-0FA3451BD8A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -109,14 +109,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>普通奖池，消耗时间币 * 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>102,2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>104,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -173,6 +165,14 @@
   </si>
   <si>
     <t>额外奖励</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通奖池，消耗时间币 * 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>102,1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -539,7 +539,7 @@
         <v>17</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
@@ -562,7 +562,7 @@
         <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
@@ -585,7 +585,7 @@
         <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
@@ -608,7 +608,7 @@
         <v>19</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
@@ -619,13 +619,13 @@
         <v>12</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -642,7 +642,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -650,16 +650,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -667,19 +667,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17B8BB7D-D867-43F9-AC2B-0F6F5822EBC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7451AE8-D36B-4C88-8CFC-735D7C7BAAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="35172" yWindow="-7128" windowWidth="22380" windowHeight="13332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -127,28 +127,31 @@
     <t>翻找垃圾桶有机会获得日常收获</t>
   </si>
   <si>
-    <t>101,10,650&amp;101,20,250&amp;102,1,100</t>
-  </si>
-  <si>
     <t>垃圾桶·实用补给</t>
   </si>
   <si>
     <t>翻找垃圾桶有机会获得实用补给</t>
   </si>
   <si>
-    <t>101,30,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
-  </si>
-  <si>
     <t>垃圾桶·惊喜发现</t>
   </si>
   <si>
     <t>翻找垃圾桶有机会发现稀有奖励</t>
   </si>
   <si>
-    <t>101,50,450&amp;103,5,250&amp;104,1,120&amp;105,1,100&amp;106,1,80</t>
-  </si>
-  <si>
     <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;1010,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,20,100&amp;101,50,50&amp;102,1,100&amp;5000,1,50&amp;5001,1,100&amp;5002,1,100&amp;5003,1,100&amp;5004,1,100&amp;5005,1,50</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -175,6 +178,7 @@
     <font>
       <sz val="9"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -485,17 +489,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="82.875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.5" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="82.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.44140625" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -518,7 +522,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -541,7 +545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -564,7 +568,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -587,7 +591,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1</v>
       </c>
@@ -598,13 +602,13 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>2</v>
       </c>
@@ -621,7 +625,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>3</v>
       </c>
@@ -638,7 +642,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>4</v>
       </c>
@@ -658,7 +662,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>5</v>
       </c>
@@ -668,39 +672,39 @@
       <c r="D9" t="s">
         <v>34</v>
       </c>
-      <c r="E9" t="s">
-        <v>35</v>
+      <c r="E9" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
         <v>36</v>
       </c>
-      <c r="D10" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" t="s">
-        <v>38</v>
+      <c r="E10" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
-      </c>
-      <c r="E11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>41</v>
       </c>
       <c r="F11"/>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7451AE8-D36B-4C88-8CFC-735D7C7BAAAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D254394-204A-4126-AD05-1B06FA3D276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="35172" yWindow="-7128" windowWidth="22380" windowHeight="13332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -139,10 +139,6 @@
     <t>翻找垃圾桶有机会发现稀有奖励</t>
   </si>
   <si>
-    <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;1010,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -152,6 +148,10 @@
   </si>
   <si>
     <t>101,20,100&amp;101,50,50&amp;102,1,100&amp;5000,1,50&amp;5001,1,100&amp;5002,1,100&amp;5003,1,100&amp;5004,1,100&amp;5005,1,50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;102,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +602,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
@@ -673,7 +673,7 @@
         <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -689,7 +689,7 @@
         <v>36</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -705,7 +705,7 @@
         <v>38</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D254394-204A-4126-AD05-1B06FA3D276B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E056029-CE9F-4CA1-B63A-0F69B0DF1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="35172" yWindow="-7128" windowWidth="22380" windowHeight="13332" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>##var</t>
   </si>
@@ -89,9 +89,6 @@
   </si>
   <si>
     <t>神秘转盘，消耗转盘币 * 1</t>
-  </si>
-  <si>
-    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;,4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
   </si>
   <si>
     <t>104,1</t>
@@ -147,11 +144,19 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,20,100&amp;101,50,50&amp;102,1,100&amp;5000,1,50&amp;5001,1,100&amp;5002,1,100&amp;5003,1,100&amp;5004,1,100&amp;5005,1,50</t>
+    <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;102,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;102,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
+    <t>101,20,100&amp;101,50,90&amp;102,1,100&amp;3002,1,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,1,1000&amp;1001,3,500&amp;3000,1,50&amp;3001,1,1000&amp;3002,1,1000&amp;3002,2,1000&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -602,7 +607,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
@@ -619,10 +624,10 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -630,16 +635,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -647,19 +652,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -667,10 +672,10 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
         <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>34</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>41</v>
@@ -683,13 +688,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" t="s">
         <v>35</v>
       </c>
-      <c r="D10" t="s">
-        <v>36</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -699,13 +704,13 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
       </c>
-      <c r="D11" t="s">
-        <v>38</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E056029-CE9F-4CA1-B63A-0F69B0DF1006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07662903-30CD-46F4-AD39-502AFA6F14C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-8592" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,10,30&amp;101,50,20&amp;101,100,10&amp;101,500,5&amp;1010,1,10&amp;102,2,5&amp;1011,1,4&amp;1050,1,4&amp;2000,1,2&amp;3000,1,10&amp;6030,1,10&amp;5000,1,5&amp;5001,1,5&amp;5002,1,5&amp;5003,1,5&amp;5004,1,5&amp;5005,1,2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>101,20,100&amp;101,50,90&amp;102,1,100&amp;3002,1,10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -156,7 +152,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,1000&amp;1001,3,500&amp;3000,1,50&amp;3001,1,1000&amp;3002,1,1000&amp;3002,2,1000&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
+    <t>1000,1,1000&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20&amp;6020,1,10</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -494,17 +494,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="51.88671875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="82.88671875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="13.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="44.44140625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13.5" style="2" customWidth="1"/>
+    <col min="4" max="4" width="51.875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="82.875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="44.5" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -527,7 +527,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -550,7 +550,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -573,7 +573,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -596,7 +596,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -607,13 +607,13 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -624,13 +624,13 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -641,13 +641,13 @@
         <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
@@ -667,7 +667,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
@@ -678,12 +678,12 @@
         <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
@@ -699,7 +699,7 @@
       <c r="F10"/>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>7</v>
       </c>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07662903-30CD-46F4-AD39-502AFA6F14C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE6F29-E5A8-4D77-B96D-F38E54831EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -144,10 +144,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,20,100&amp;101,50,90&amp;102,1,100&amp;3002,1,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -156,7 +152,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20&amp;6020,1,10</t>
+    <t>101,20,100&amp;101,50,100&amp;1010,1,100&amp;3020,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -624,7 +624,7 @@
         <v>22</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>23</v>
@@ -641,7 +641,7 @@
         <v>25</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>26</v>
@@ -678,7 +678,7 @@
         <v>33</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4FE6F29-E5A8-4D77-B96D-F38E54831EE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF08CDB-4E7E-455C-A7FF-65E1E4BC06FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
   <si>
     <t>##var</t>
   </si>
@@ -157,6 +157,26 @@
   </si>
   <si>
     <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动售货机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3020,1,500&amp;3020,2,300&amp;3020,3,100&amp;1010,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗失的钱包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,88,500&amp;101,188,300&amp;101,288,100</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -210,7 +230,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -218,6 +238,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -493,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
@@ -715,6 +739,37 @@
       <c r="F11"/>
       <c r="G11"/>
     </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B12" s="2">
+        <v>8</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B13" s="2">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDF08CDB-4E7E-455C-A7FF-65E1E4BC06FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88E11B2-8B04-4723-87BA-471F3EA97B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -85,98 +85,123 @@
     <t>102,1</t>
   </si>
   <si>
+    <t>神秘转盘，消耗转盘币 * 1</t>
+  </si>
+  <si>
+    <t>104,1</t>
+  </si>
+  <si>
+    <t>时光秘匣</t>
+  </si>
+  <si>
+    <t>时光秘匣，消耗秘匣币 * 1</t>
+  </si>
+  <si>
+    <t>105,1</t>
+  </si>
+  <si>
+    <t>时光星阵</t>
+  </si>
+  <si>
+    <t>时光星阵，消耗星阵币 * 1</t>
+  </si>
+  <si>
+    <t>1001,1,500&amp;1002,1,500&amp;1003,1,500&amp;1004,1,500</t>
+  </si>
+  <si>
+    <t>106,1</t>
+  </si>
+  <si>
+    <t>1001,5&amp;1002,10&amp;1003,20&amp;1004,50&amp;1001,5&amp;1002,10&amp;1003,20&amp;1004,50</t>
+  </si>
+  <si>
+    <t>垃圾桶·日常收获</t>
+  </si>
+  <si>
+    <t>翻找垃圾桶有机会获得日常收获</t>
+  </si>
+  <si>
+    <t>垃圾桶·实用补给</t>
+  </si>
+  <si>
+    <t>翻找垃圾桶有机会获得实用补给</t>
+  </si>
+  <si>
+    <t>垃圾桶·惊喜发现</t>
+  </si>
+  <si>
+    <t>翻找垃圾桶有机会发现稀有奖励</t>
+  </si>
+  <si>
+    <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,20,100&amp;101,50,100&amp;1010,1,100&amp;3020,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自动售货机</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3020,1,500&amp;3020,2,300&amp;3020,3,100&amp;1010,1,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>遗失的钱包</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,88,500&amp;101,188,300&amp;101,288,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>流浪猫食物盆</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3010,1,100&amp;3011,1,10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>5005,1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社区募捐箱</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3020,1,500&amp;3020,2,100&amp;3020,3,50&amp;1010,1,50</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>101,30</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>神秘转盘</t>
-  </si>
-  <si>
-    <t>神秘转盘，消耗转盘币 * 1</t>
-  </si>
-  <si>
-    <t>104,1</t>
-  </si>
-  <si>
-    <t>时光秘匣</t>
-  </si>
-  <si>
-    <t>时光秘匣，消耗秘匣币 * 1</t>
-  </si>
-  <si>
-    <t>105,1</t>
-  </si>
-  <si>
-    <t>时光星阵</t>
-  </si>
-  <si>
-    <t>时光星阵，消耗星阵币 * 1</t>
-  </si>
-  <si>
-    <t>1001,1,500&amp;1002,1,500&amp;1003,1,500&amp;1004,1,500</t>
-  </si>
-  <si>
-    <t>106,1</t>
-  </si>
-  <si>
-    <t>1001,5&amp;1002,10&amp;1003,20&amp;1004,50&amp;1001,5&amp;1002,10&amp;1003,20&amp;1004,50</t>
-  </si>
-  <si>
-    <t>垃圾桶·日常收获</t>
-  </si>
-  <si>
-    <t>翻找垃圾桶有机会获得日常收获</t>
-  </si>
-  <si>
-    <t>垃圾桶·实用补给</t>
-  </si>
-  <si>
-    <t>翻找垃圾桶有机会获得实用补给</t>
-  </si>
-  <si>
-    <t>垃圾桶·惊喜发现</t>
-  </si>
-  <si>
-    <t>翻找垃圾桶有机会发现稀有奖励</t>
-  </si>
-  <si>
-    <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000,1,1000&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,20,100&amp;101,50,100&amp;1010,1,100&amp;3020,1,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动售货机</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3020,1,500&amp;3020,2,300&amp;3020,3,100&amp;1010,1,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>遗失的钱包</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,88,500&amp;101,188,300&amp;101,288,100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,1,1000&amp;1000,3,1000&amp;1000,5,1000&amp;1001,1,500&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -517,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
@@ -631,7 +656,7 @@
         <v>19</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>20</v>
@@ -642,16 +667,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -659,16 +684,16 @@
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
@@ -676,19 +701,19 @@
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="G8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -696,13 +721,13 @@
         <v>5</v>
       </c>
       <c r="C9" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
-        <v>33</v>
-      </c>
       <c r="E9" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
@@ -712,13 +737,13 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
         <v>34</v>
       </c>
-      <c r="D10" t="s">
-        <v>35</v>
-      </c>
       <c r="E10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
@@ -728,13 +753,13 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" t="s">
-        <v>37</v>
-      </c>
       <c r="E11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>
@@ -744,16 +769,16 @@
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="F12" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
@@ -761,13 +786,47 @@
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E14" s="1" t="s">
         <v>48</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B15" s="2">
+        <v>11</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B88E11B2-8B04-4723-87BA-471F3EA97B79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4478BCC5-FCFF-482A-9FBF-12866BDD291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -201,7 +201,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1000,1,1000&amp;1000,3,1000&amp;1000,5,1000&amp;1001,1,500&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4028,1,500&amp;4023,1,1000</t>
+    <t>1000,1,1000&amp;1000,3,1000&amp;1000,5,1000&amp;1001,1,500&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4023,1,1000</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4478BCC5-FCFF-482A-9FBF-12866BDD291D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB755169-FAB6-4259-8079-1E725D892EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
   <si>
     <t>##var</t>
   </si>
@@ -43,6 +43,21 @@
     <t>additionRewards</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
+    <t>minRewardCount</t>
+  </si>
+  <si>
+    <t>maxRewardCount</t>
+  </si>
+  <si>
+    <t>minPrice</t>
+  </si>
+  <si>
+    <t>maxPrice</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -76,18 +91,42 @@
     <t>额外奖励</t>
   </si>
   <si>
+    <t>集装箱图标路径</t>
+  </si>
+  <si>
+    <t>最小奖品数量</t>
+  </si>
+  <si>
+    <t>最大奖品数量</t>
+  </si>
+  <si>
+    <t>最低模拟币价格</t>
+  </si>
+  <si>
+    <t>最高模拟币价格</t>
+  </si>
+  <si>
     <t>普通奖池</t>
   </si>
   <si>
     <t>普通奖池，消耗时间币 * 1</t>
   </si>
   <si>
+    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
+  </si>
+  <si>
     <t>102,1</t>
   </si>
   <si>
+    <t>神秘转盘</t>
+  </si>
+  <si>
     <t>神秘转盘，消耗转盘币 * 1</t>
   </si>
   <si>
+    <t>1000,1,1000&amp;1000,3,1000&amp;1000,5,1000&amp;1001,1,500&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4023,1,1000</t>
+  </si>
+  <si>
     <t>104,1</t>
   </si>
   <si>
@@ -97,6 +136,9 @@
     <t>时光秘匣，消耗秘匣币 * 1</t>
   </si>
   <si>
+    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+  </si>
+  <si>
     <t>105,1</t>
   </si>
   <si>
@@ -121,87 +163,127 @@
     <t>翻找垃圾桶有机会获得日常收获</t>
   </si>
   <si>
+    <t>101,20,100&amp;101,50,100&amp;1010,1,100&amp;3020,1,100</t>
+  </si>
+  <si>
     <t>垃圾桶·实用补给</t>
   </si>
   <si>
     <t>翻找垃圾桶有机会获得实用补给</t>
   </si>
   <si>
+    <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
+  </si>
+  <si>
     <t>垃圾桶·惊喜发现</t>
   </si>
   <si>
     <t>翻找垃圾桶有机会发现稀有奖励</t>
   </si>
   <si>
-    <t>101,88,450&amp;1000,1,300&amp;1001,1,170&amp;1050,1,80</t>
+    <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
+  </si>
+  <si>
+    <t>自动售货机</t>
+  </si>
+  <si>
+    <t>3020,1,500&amp;3020,2,300&amp;3020,3,100&amp;1010,1,100</t>
+  </si>
+  <si>
+    <t>101,50</t>
+  </si>
+  <si>
+    <t>遗失的钱包</t>
+  </si>
+  <si>
+    <t>101,88,500&amp;101,188,300&amp;101,288,100</t>
+  </si>
+  <si>
+    <t>流浪猫食物盆</t>
+  </si>
+  <si>
+    <t>3010,1,100&amp;3011,1,10</t>
+  </si>
+  <si>
+    <t>5005,1</t>
+  </si>
+  <si>
+    <t>社区募捐箱</t>
+  </si>
+  <si>
+    <t>3020,1,500&amp;3020,2,100&amp;3020,3,50&amp;1010,1,50</t>
+  </si>
+  <si>
+    <t>101,30</t>
+  </si>
+  <si>
+    <t>随机获得基础补给</t>
+  </si>
+  <si>
+    <t>101,50,450&amp;101,100,300&amp;1000,1,150&amp;3020,1,100</t>
+  </si>
+  <si>
+    <t>随机获得实用补给</t>
+  </si>
+  <si>
+    <t>101,100,350&amp;101,188,250&amp;1000,1,180&amp;1001,1,120&amp;3020,1,70&amp;1050,1,30</t>
+  </si>
+  <si>
+    <t>随机获得进阶物资</t>
+  </si>
+  <si>
+    <t>101,188,300&amp;101,288,200&amp;1001,1,160&amp;3010,1,100&amp;3020,2,90&amp;1010,1,50&amp;1050,1,30</t>
+  </si>
+  <si>
+    <t>随机获得珍贵物资</t>
+  </si>
+  <si>
+    <t>101,288,260&amp;101,500,180&amp;1002,1,130&amp;1003,1,80&amp;3010,1,110&amp;3011,1,60&amp;1010,1,100&amp;1011,1,40</t>
+  </si>
+  <si>
+    <t>随机获得稀有补给</t>
+  </si>
+  <si>
+    <t>101,500,220&amp;101,888,170&amp;1003,1,120&amp;1004,1,70&amp;3011,1,120&amp;1010,2,100&amp;1011,1,70&amp;1051,1,30</t>
+  </si>
+  <si>
+    <t>一阶集装箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
+    <t>二阶集装箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1,100&amp;1002,1,100&amp;1003,1,100&amp;1004,1,100&amp;3000,1,100&amp;4000,1,100&amp;4001,1,100&amp;4002,1,100&amp;4003,1,100&amp;4004,1,100&amp;4005,1,100&amp;4006,1,100&amp;4007,1,100&amp;4008,1,100&amp;4009,1,100&amp;4010,1,100&amp;4011,1,100&amp;4012,1,100</t>
+    <t>三阶集装箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,20,100&amp;101,50,100&amp;1010,1,100&amp;3020,1,100</t>
+    <t>四阶集装箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,20,100&amp;101,50,50&amp;101,100,50&amp;101,500,10&amp;1010,2,50&amp;1011,1,10&amp;1050,1,100&amp;2000,1,10&amp;3000,1,50&amp;3020,1,100&amp;3020,2,100&amp;3020,5,20</t>
+    <t>五阶集装箱</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>自动售货机</t>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[port_container_1]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,50</t>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[port_container_2]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3020,1,500&amp;3020,2,300&amp;3020,3,100&amp;1010,1,100</t>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[port_container_3]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>遗失的钱包</t>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[port_container_4]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>101,88,500&amp;101,188,300&amp;101,288,100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>流浪猫食物盆</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3010,1,100&amp;3011,1,10</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>5005,1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>社区募捐箱</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3020,1,500&amp;3020,2,100&amp;3020,3,50&amp;1010,1,50</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>101,30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>神秘转盘</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000,1,1000&amp;1000,3,1000&amp;1000,5,1000&amp;1001,1,500&amp;1001,3,500&amp;3000,1,50&amp;3001,1,10&amp;3001,1,10&amp;1050,1,1000&amp;1051,1,1000&amp;4000,1,1000&amp;4001,1,1000&amp;4023,1,1000</t>
+    <t>Assets/Art/Community/SpriteAtlas.spriteatlasv2[port_container_5]</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -255,7 +337,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -264,9 +346,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -542,7 +621,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="7.125" style="2" customWidth="1"/>
@@ -551,9 +630,10 @@
     <col min="5" max="5" width="82.875" style="2" customWidth="1"/>
     <col min="6" max="6" width="13.75" style="2" customWidth="1"/>
     <col min="7" max="7" width="44.5" style="2" customWidth="1"/>
+    <col min="8" max="8" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -575,258 +655,595 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
+        <v>13</v>
+      </c>
+      <c r="K2" t="s">
+        <v>13</v>
+      </c>
+      <c r="L2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>22</v>
+      </c>
+      <c r="H4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>44</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F9"/>
       <c r="G9"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F10"/>
       <c r="G10"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="F11"/>
       <c r="G11"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B12" s="2">
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B12">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="2">
+        <v>56</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B13">
         <v>9</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="2">
+        <v>58</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B14">
         <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B15" s="2">
+        <v>61</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B15">
         <v>11</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
         <v>50</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>52</v>
+      <c r="L16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" t="s">
+        <v>68</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="I17">
+        <v>2</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+      <c r="L17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18">
+        <v>14</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D18" t="s">
+        <v>69</v>
+      </c>
+      <c r="E18" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18">
+        <v>3</v>
+      </c>
+      <c r="J18">
+        <v>6</v>
+      </c>
+      <c r="K18">
+        <v>200</v>
+      </c>
+      <c r="L18">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19">
+        <v>8</v>
+      </c>
+      <c r="K19">
+        <v>400</v>
+      </c>
+      <c r="L19">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B20">
+        <v>16</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>10</v>
+      </c>
+      <c r="K20">
+        <v>800</v>
+      </c>
+      <c r="L20">
+        <v>1600</v>
       </c>
     </row>
   </sheetData>

--- a/MiniTemplate/Datas/lottery.xlsx
+++ b/MiniTemplate/Datas/lottery.xlsx
@@ -482,7 +482,7 @@
           <t>maxPrice</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>grandPrize</t>
         </is>
@@ -549,7 +549,7 @@
           <t>int</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>string</t>
         </is>
@@ -616,7 +616,7 @@
           <t>c,s</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
@@ -683,7 +683,7 @@
           <t>最高模拟币价格</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>大奖配置(道具id,数量,保底次数)</t>
         </is>
@@ -725,7 +725,7 @@
       <c r="L5" s="0" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="M5" s="0" t="inlineStr">
         <is>
           <t>3003,1,30</t>
         </is>
@@ -931,7 +931,7 @@
       </c>
       <c r="E11" s="1" t="inlineStr">
         <is>
-          <t>101,188,450&amp;104,1,120&amp;105,1,50&amp;106,1,20</t>
+          <t>101,188,450&amp;104,1,120&amp;106,1,20</t>
         </is>
       </c>
       <c r="F11" s="0" t="n"/>
